--- a/artfynd/A 43319-2025 artfynd.xlsx
+++ b/artfynd/A 43319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887648</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887674</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887635</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887641</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887651</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887655</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887672</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887677</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887680</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887733</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2071,6 +2136,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045757</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045755</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984226</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984227</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984244</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2595,6 +2685,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887637</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887650</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2809,6 +2909,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887662</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2916,6 +3021,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887678</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3023,6 +3133,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887679</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3130,6 +3245,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887688</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3237,6 +3357,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887730</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3344,6 +3469,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887734</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3451,6 +3581,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887735</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3558,6 +3693,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887640</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3665,6 +3805,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887668</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3772,6 +3917,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887642</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3879,6 +4029,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887649</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3986,6 +4141,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887676</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4087,6 +4247,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984225</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4194,6 +4359,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887636</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4301,6 +4471,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887628</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4408,6 +4583,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887631</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4515,6 +4695,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887633</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4622,6 +4807,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887644</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4729,6 +4919,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887664</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4836,6 +5031,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887685</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4943,6 +5143,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887639</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5050,6 +5255,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887653</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5157,6 +5367,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887682</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5264,6 +5479,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887689</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5371,6 +5591,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887727</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5478,6 +5703,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887646</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5585,6 +5815,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887654</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5697,6 +5932,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887666</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5809,6 +6049,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887687</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5916,6 +6161,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887732</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6023,6 +6273,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887665</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6130,6 +6385,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887683</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6237,6 +6497,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887670</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6344,6 +6609,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887731</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6451,6 +6721,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887667</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6558,6 +6833,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887671</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6678,6 +6958,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887629</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6798,6 +7083,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887630</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6918,6 +7208,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887632</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7038,6 +7333,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887634</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7158,6 +7458,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887638</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7278,6 +7583,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887643</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7398,6 +7708,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887645</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7518,6 +7833,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887647</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7638,6 +7958,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887652</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7758,6 +8083,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887656</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7878,6 +8208,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887657</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7998,6 +8333,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887658</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8118,6 +8458,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887659</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8238,6 +8583,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887660</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8358,6 +8708,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887663</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8478,6 +8833,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887673</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8598,6 +8958,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887675</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8718,6 +9083,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887686</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8838,6 +9208,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887726</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8958,6 +9333,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887729</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9065,6 +9445,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887691</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9172,6 +9557,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887728</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9284,6 +9674,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887661</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9391,6 +9786,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887681</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9505,6 +9905,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045756</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9606,6 +10011,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984242</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9713,8 +10123,97 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887669</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>